--- a/backend/src/test/resources/golden/index_twse.xlsx
+++ b/backend/src/test/resources/golden/index_twse.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>日期</t>
   </si>
@@ -29,6 +29,18 @@
     <t>收盤</t>
   </si>
   <si>
+    <t>週線MA5</t>
+  </si>
+  <si>
+    <t>月線MA20</t>
+  </si>
+  <si>
+    <t>季線MA60</t>
+  </si>
+  <si>
+    <t>年線MA240</t>
+  </si>
+  <si>
     <t>2026-07-30</t>
   </si>
   <si>
@@ -43,7 +55,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -60,6 +72,17 @@
       <name val="Calibri"/>
       <sz val="13.0"/>
       <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="12.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="10"/>
     </font>
   </fonts>
   <fills count="2">
@@ -82,12 +105,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
@@ -98,7 +123,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="10.73046875" customWidth="true" bestFit="true"/>
@@ -106,6 +131,10 @@
     <col min="3" max="3" width="10.90234375" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="10.90234375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="10.90234375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="7.76953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="8.8125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="8.8125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="9.85546875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -124,29 +153,41 @@
       <c r="E1" t="s" s="1">
         <v>4</v>
       </c>
+      <c r="F1" t="s" s="1">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s" s="1">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s" s="1">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s" s="1">
+        <v>8</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>5</v>
+        <v>9</v>
       </c>
-      <c r="B2" t="n" s="4">
+      <c r="B2" t="n" s="6">
         <v>23000.0</v>
       </c>
-      <c r="C2" t="n" s="4">
+      <c r="C2" t="n" s="6">
         <v>23100.0</v>
       </c>
-      <c r="D2" t="n" s="4">
+      <c r="D2" t="n" s="6">
         <v>22900.0</v>
       </c>
-      <c r="E2" t="n" s="4">
+      <c r="E2" t="n" s="6">
         <v>23050.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>6</v>
+        <v>10</v>
       </c>
-      <c r="E3" t="n" s="4">
+      <c r="E3" t="n" s="6">
         <v>23200.0</v>
       </c>
     </row>

--- a/backend/src/test/resources/golden/index_twse.xlsx
+++ b/backend/src/test/resources/golden/index_twse.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>日期</t>
   </si>
@@ -39,6 +39,12 @@
   </si>
   <si>
     <t>年線MA240</t>
+  </si>
+  <si>
+    <t>成交股數</t>
+  </si>
+  <si>
+    <t>成交金額</t>
   </si>
   <si>
     <t>2026-07-30</t>
@@ -105,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
@@ -117,13 +123,14 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="10.73046875" customWidth="true" bestFit="true"/>
@@ -135,6 +142,8 @@
     <col min="7" max="7" width="8.8125" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="8.8125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="9.85546875" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="7.2890625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="7.2890625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -165,10 +174,16 @@
       <c r="I1" t="s" s="1">
         <v>8</v>
       </c>
+      <c r="J1" t="s" s="1">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s" s="1">
+        <v>10</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" t="n" s="6">
         <v>23000.0</v>
@@ -185,7 +200,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n" s="6">
         <v>23200.0</v>
